--- a/pacjenci/RENATA PIROWSKA.xlsx
+++ b/pacjenci/RENATA PIROWSKA.xlsx
@@ -483,7 +483,11 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -523,7 +527,11 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -563,7 +571,11 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Do oceny</t>

--- a/pacjenci/RENATA PIROWSKA.xlsx
+++ b/pacjenci/RENATA PIROWSKA.xlsx
@@ -413,191 +413,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>27.05.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy rozlany. Ocena zaawansowania klinicznego.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 86mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W obu jamach opłucnowych   Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w części przedodźwiernikowej żołądka, SUV max do 4,0 - w pierwszej kolejności czynnościowe. Aktywny metabolicznie naciek w miednicy mniejszej obejmujący pętle jelit, macicę, pochwę, pęcherz moczowy, przylegające węzły chłonne o łącznym wymiarze wg PET 86x116x151mm, SUV max do 23,7. Aktywność metaboliczna w topografi pętli jelit (?) położonych do przodu od  głównej masy guza, SUV max do 6,6 - naciek chłoniakowy? zmiany czynnościowe z ucisku? Aktywny metabolicznie węzeł chłonny pachwinowy lewy średnicy wg PET 26mm, SUV max 10,9. Pobudzony metabolicznie węzeł chłonny biodrowy zewnętrzny prawy wielkości 20x13mm, SUV max 4,6 [Im fuz 232] Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Pęcherzyk żółciowy cienkościenny z uwapnionym na obwodzie konkrementem w zakresie trzonu ok. 23x15mm.  W odnodze bocznej nadnercza prawego guzek ok. 16x12mm - do oceny z kontrastem i.v. Nefrostomia po stronie lewej. UKM nerki prawej poszerzony. Cewnik w pęcherzu moczowym.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym, zwłaszcza w trzonie S1 - konieczna kontrola. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Skolioza. Blok kostny Th3/Th4. Dyskopatia C5/6.  Wartości referencyjne: MBPS SUVmax 2,0, Prawy płat wątroby SUVmax do 4,6.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono rozległy aktywny metabolicznie naciek chłoniakowy w obrębie miednicy mniejszej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>23.7</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>17.08.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy rozlany. Ocena odpowiedzi po 3 cyklach chemioimmunoterapii.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  58min od podania 18F-FDG. Glikemia: 101mg%</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w nadwpustowej części żołądka, SUV max do 3,8 - w pierwszej kolejności czynnościowe. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Pęcherzyk żółciowy cienkościenny z uwapnionym na obwodzie konkrementem w zakresie trzonu ok. 23x15mm.  W odnodze bocznej nadnercza prawego guzek ok. 16x12mm - do oceny z kontrastem i.v. Węzły chłonne pachwinowe średnicy do 15mm. Przy lewym mięśniu gruszkowatym widoczne niewielkie pasmo miękkotkankowe grubości 6mm - do kontroli.  Układ kostny: Rozlany metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Skolioza. Blok kostny Th3/Th4. Dyskopatia C5/6.  Inne: Rozlana aktywność metaboliczna w mięśniach grzbietu po stronie prawej, SUV max do 4,1 - w pierwszej kolejności czynnościowe.  Wartości referencyjne: MBPS SUVmax 2,3, Prawy płat wątroby SUVmax do 3,1.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej  na stosowane leczenie.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>4.1</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>09.11.2021</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy rozlany. Ocena remisji choroby po zakończeniu chemioterapii.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  58min od podania 18F-FDG. Glikemia: 95mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja lewej zatoki czołowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włóknisto-niedodmowe u podstawy płata górnego płuca lewego. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w nadwpustowej części żołądka, SUV max do 3,3 - w pierwszej kolejności czynnościowe. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Pęcherzyk żółciowy cienkościenny z uwapnionym na obwodzie konkrementem wielkości ok. 23x18mm.  W odnodze bocznej nadnercza prawego guzek wielkości ok. 15x12mm. Węzły chłonne pachwinowe średnicy do 12mm. Przy lewym mięśniu gruszkowatym widoczne niewielkie pasmo miękkotkankowe o szerokości ok 6mm - do kontroli.  Układ kostny: Rozlany metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza: prawowypukła w odcinku piersiowym oraz lewowypukła w odcinku lędźwiowym kręgosłupa. Cecy niestabilności i dyskopatie w odcinku szyjnym kręgosłupa - ciasna na poziomie C5/C6. Blok kostny na poziomie Th3/Th4, ze szczątkową, sklerotyczną tarczą międzykręgową. Kątowe ułożenie kości krzyżowej.   Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 3,1.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnej metabolicznie choroby chłoniakowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>3.3</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/RENATA PIROWSKA.xlsx
+++ b/pacjenci/RENATA PIROWSKA.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 86mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W obu jamach opłucnowych   Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w części przedodźwiernikowej żołądka, SUV max do 4,0 - w pierwszej kolejności czynnościowe. Aktywny metabolicznie naciek w miednicy mniejszej obejmujący pętle jelit, macicę, pochwę, pęcherz moczowy, przylegające węzły chłonne o łącznym wymiarze wg PET 86x116x151mm, SUV max do 23,7. Aktywność metaboliczna w topografi pętli jelit (?) położonych do przodu od  głównej masy guza, SUV max do 6,6 - naciek chłoniakowy? zmiany czynnościowe z ucisku? Aktywny metabolicznie węzeł chłonny pachwinowy lewy średnicy wg PET 26mm, SUV max 10,9. Pobudzony metabolicznie węzeł chłonny biodrowy zewnętrzny prawy wielkości 20x13mm, SUV max 4,6 [Im fuz 232] Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Pęcherzyk żółciowy cienkościenny z uwapnionym na obwodzie konkrementem w zakresie trzonu ok. 23x15mm.  W odnodze bocznej nadnercza prawego guzek ok. 16x12mm - do oceny z kontrastem i.v. Nefrostomia po stronie lewej. UKM nerki prawej poszerzony. Cewnik w pęcherzu moczowym.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym, zwłaszcza w trzonie S1 - konieczna kontrola. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Skolioza. Blok kostny Th3/Th4. Dyskopatia C5/6.  Wartości referencyjne: MBPS SUVmax 2,0, Prawy płat wątroby SUVmax do 4,6.</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W obu jamach opłucnowych</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Rozlanie zwiększony metabolizm FDG w części przedodźwiernikowej żołądka, SUV max do 4,0 - w pierwszej kolejności czynnościowe. Aktywny metabolicznie naciek w miednicy mniejszej obejmujący pętle jelit, macicę, pochwę, pęcherz moczowy, przylegające węzły chłonne o łącznym wymiarze wg PET 86x116x151mm, SUV max do 23,7. Aktywność metaboliczna w topografi pętli jelit (?) położonych do przodu od  głównej masy guza, SUV max do 6,6 - naciek chłoniakowy? zmiany czynnościowe z ucisku? Aktywny metabolicznie węzeł chłonny pachwinowy lewy średnicy wg PET 26mm, SUV max 10,9. Pobudzony metabolicznie węzeł chłonny biodrowy zewnętrzny prawy wielkości 20x13mm, SUV max 4,6 [Im fuz 232] Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Pęcherzyk żółciowy cienkościenny z uwapnionym na obwodzie konkrementem w zakresie trzonu ok. 23x15mm.  W odnodze bocznej nadnercza prawego guzek ok. 16x12mm - do oceny z kontrastem i.v. Nefrostomia po stronie lewej. UKM nerki prawej poszerzony. Cewnik w pęcherzu moczowym.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym, zwłaszcza w trzonie S1 - konieczna kontrola. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Skolioza. Blok kostny Th3/Th4. Dyskopatia C5/6.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono rozległy aktywny metabolicznie naciek chłoniakowy w obrębie miednicy mniejszej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>23.7</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  58min od podania 18F-FDG. Glikemia: 101mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w nadwpustowej części żołądka, SUV max do 3,8 - w pierwszej kolejności czynnościowe. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Pęcherzyk żółciowy cienkościenny z uwapnionym na obwodzie konkrementem w zakresie trzonu ok. 23x15mm.  W odnodze bocznej nadnercza prawego guzek ok. 16x12mm - do oceny z kontrastem i.v. Węzły chłonne pachwinowe średnicy do 15mm. Przy lewym mięśniu gruszkowatym widoczne niewielkie pasmo miękkotkankowe grubości 6mm - do kontroli.  Układ kostny: Rozlany metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Skolioza. Blok kostny Th3/Th4. Dyskopatia C5/6.  Inne: Rozlana aktywność metaboliczna w mięśniach grzbietu po stronie prawej, SUV max do 4,1 - w pierwszej kolejności czynnościowe.  Wartości referencyjne: MBPS SUVmax 2,3, Prawy płat wątroby SUVmax do 3,1.</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Rozlanie zwiększony metabolizm FDG w nadwpustowej części żołądka, SUV max do 3,8 - w pierwszej kolejności czynnościowe. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Pęcherzyk żółciowy cienkościenny z uwapnionym na obwodzie konkrementem w zakresie trzonu ok. 23x15mm.  W odnodze bocznej nadnercza prawego guzek ok. 16x12mm - do oceny z kontrastem i.v. Węzły chłonne pachwinowe średnicy do 15mm. Przy lewym mięśniu gruszkowatym widoczne niewielkie pasmo miękkotkankowe grubości 6mm - do kontroli.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Rozlany metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Skolioza. Blok kostny Th3/Th4. Dyskopatia C5/6.  Inne: Rozlana aktywność metaboliczna w mięśniach grzbietu po stronie prawej, SUV max do 4,1 - w pierwszej kolejności czynnościowe.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej  na stosowane leczenie.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>4.1</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  58min od podania 18F-FDG. Glikemia: 95mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja lewej zatoki czołowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włóknisto-niedodmowe u podstawy płata górnego płuca lewego. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w nadwpustowej części żołądka, SUV max do 3,3 - w pierwszej kolejności czynnościowe. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Pęcherzyk żółciowy cienkościenny z uwapnionym na obwodzie konkrementem wielkości ok. 23x18mm.  W odnodze bocznej nadnercza prawego guzek wielkości ok. 15x12mm. Węzły chłonne pachwinowe średnicy do 12mm. Przy lewym mięśniu gruszkowatym widoczne niewielkie pasmo miękkotkankowe o szerokości ok 6mm - do kontroli.  Układ kostny: Rozlany metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza: prawowypukła w odcinku piersiowym oraz lewowypukła w odcinku lędźwiowym kręgosłupa. Cecy niestabilności i dyskopatie w odcinku szyjnym kręgosłupa - ciasna na poziomie C5/C6. Blok kostny na poziomie Th3/Th4, ze szczątkową, sklerotyczną tarczą międzykręgową. Kątowe ułożenie kości krzyżowej.   Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 3,1.</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja lewej zatoki czołowej.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włóknisto-niedodmowe u podstawy płata górnego płuca lewego. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Rozlanie zwiększony metabolizm FDG w nadwpustowej części żołądka, SUV max do 3,3 - w pierwszej kolejności czynnościowe. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Pęcherzyk żółciowy cienkościenny z uwapnionym na obwodzie konkrementem wielkości ok. 23x18mm.  W odnodze bocznej nadnercza prawego guzek wielkości ok. 15x12mm. Węzły chłonne pachwinowe średnicy do 12mm. Przy lewym mięśniu gruszkowatym widoczne niewielkie pasmo miękkotkankowe o szerokości ok 6mm - do kontroli.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Rozlany metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza: prawowypukła w odcinku piersiowym oraz lewowypukła w odcinku lędźwiowym kręgosłupa. Cecy niestabilności i dyskopatie w odcinku szyjnym kręgosłupa - ciasna na poziomie C5/C6. Blok kostny na poziomie Th3/Th4, ze szczątkową, sklerotyczną tarczą międzykręgową. Kątowe ułożenie kości krzyżowej.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnej metabolicznie choroby chłoniakowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>3.3</v>
       </c>
     </row>
